--- a/bkp/ofertas_consolidadas.xlsx
+++ b/bkp/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,771 +453,771 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105007</v>
+        <v>105470</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABOBORA CABOTIA KG</t>
+          <t>BOVINO - ACEM KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104937</v>
+        <v>105459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105023</v>
+        <v>105458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.59</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104998</v>
+        <v>105471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BANANA TERRA KG</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104903</v>
+        <v>105449</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BATATA DOCE ROSA KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105010</v>
+        <v>105475</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>BOVINO - MUSCULO KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.89</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105001</v>
+        <v>105453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>FILE MIGNON KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104919</v>
+        <v>105062</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104862</v>
+        <v>106054</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.49</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104931</v>
+        <v>193650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.390000000000001</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104944</v>
+        <v>194792</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.39</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104928</v>
+        <v>119923</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104883</v>
+        <v>104602</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MANGA TOMY KG</t>
+          <t>COXA SADIA FRANGO PACOTE 1KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104947</v>
+        <v>306504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.79</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104996</v>
+        <v>108788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>113290</v>
+        <v>108773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MELAO AMARELO REI / REDINHA KG</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>239921</v>
+        <v>261357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVOS BRANCOS CARTELA 30 UNID</t>
+          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.65</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>104992</v>
+        <v>108771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>104961</v>
+        <v>170464</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.49</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>104890</v>
+        <v>138538</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UVA RED GLOBE NACIONAL KG</t>
+          <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105460</v>
+        <v>127328</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105450</v>
+        <v>105842</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOVINO - ALCATRA KG</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34.99</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105459</v>
+        <v>107259</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
+          <t>CORACAO FRANGO KG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>239334</v>
+        <v>105838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.99</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>105468</v>
+        <v>105840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>105435</v>
+        <v>109597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>107260</v>
+        <v>105853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.99</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>305039</v>
+        <v>152244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>GALINHA PESADA NOROESTE CONG KG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>105062</v>
+        <v>228422</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>106032</v>
+        <v>132881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>SALSICHA FRIATO KG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>318330</v>
+        <v>298239</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100431</v>
+        <v>181416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.19</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>102242</v>
+        <v>107394</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>AMAC ROUPAS YPE 2L CARINHO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>116139</v>
+        <v>106712</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>AMAC ROUPAS YPE 2LT TERNURA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>107395</v>
+        <v>107413</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>AMACIANTE YPE 2L DELICADO BRANCO</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>100038</v>
+        <v>179914</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>27.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>148775</v>
+        <v>100038</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>199440</v>
+        <v>325990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>19.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>100040</v>
+        <v>148775</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
+          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>24.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>250013</v>
+        <v>100020</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6.59</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>286197</v>
+        <v>325991</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+          <t>ARROZ PARBOLIZADO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>114037</v>
+        <v>326645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>252992</v>
+        <v>111378</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1227,523 +1227,1261 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>298701</v>
+        <v>261728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.19</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>242930</v>
+        <v>286197</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>110330</v>
+        <v>102085</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.19</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>123791</v>
+        <v>101137</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>123792</v>
+        <v>287369</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>123793</v>
+        <v>170451</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>123795</v>
+        <v>242930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>123796</v>
+        <v>317589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+          <t>CREME DE LEITE UHT ITALAC 200GR 10% DE G</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>123797</v>
+        <v>208281</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+          <t>DES AERO MOOD MEN 150ML</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>100423</v>
+        <v>208304</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML COCO</t>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>100419</v>
+        <v>208280</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+          <t>DES AERO MOOD WOMEN 150ML</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>220037</v>
+        <v>214812</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+          <t>DESINFETANTE +FAMILIA 2L CITRONELA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>204461</v>
+        <v>214065</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+          <t>DESINFETANTE +FAMILIA 2L FLORAL</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100420</v>
+        <v>107851</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+          <t>DESINFETANTE +FAMILIA 2L HERBAL</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>100417</v>
+        <v>109602</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML MACA</t>
+          <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>106661</v>
+        <v>100316</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+          <t>DESINFETANTE +FAMILIA 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>167686</v>
+        <v>100315</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
+          <t>DESINFETANTE +FAMILIA 2LT PINHO</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5.89</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100014</v>
+        <v>312369</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>106922</v>
+        <v>312371</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>42.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>131884</v>
+        <v>312370</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.39</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>130920</v>
+        <v>312366</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.89</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>167128</v>
+        <v>312367</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8.789999999999999</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>316048</v>
+        <v>312368</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
+          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>326954</v>
+        <v>298932</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>289451</v>
+        <v>298931</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>29.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>228234</v>
+        <v>298930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>106831</v>
+        <v>298929</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>111010</v>
+        <v>298928</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR S/PIMENTA</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>100884</v>
+        <v>298933</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D73" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>298927</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>311881</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>119826</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>111567</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>110352</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>110353</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>252617</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>106663</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>113911</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>112163</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>113914</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>312365</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>312364</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>102287</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>100780</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EXT TOMATE OLE 190GR CP</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>100110</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>100014</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FEIJAO GOL CORES 1KG</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>163918</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>284913</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOFLOKOS 400GR</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>100119</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>100789</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR PICANTE</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>100785</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>155080</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>174382</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>170363</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>106922</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>156422</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>131884</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>101726</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>149122</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>221945</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>MILHO VERDE LATA 170G PREDILECTA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>106680</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OLEO SOJA SOYA  900ML</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>128920</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>104410</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>257710</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>261980</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>100705</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
         <v>5.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>100693</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>100876</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>14.99</v>
       </c>
     </row>
   </sheetData>
